--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_los_rios.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_los_rios.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:37</t>
+    <t xml:space="preserve">2026-09-09 19:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_los_rios.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_los_rios.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:55</t>
+    <t xml:space="preserve">2026-09-18 17:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_los_rios.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_los_rios.xlsx
@@ -30,42 +30,42 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Máfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futrono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panguipulli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Unión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paillaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Bueno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lago Ranco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariquina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Valdivia</t>
   </si>
   <si>
-    <t xml:space="preserve">Corral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariquina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lago Ranco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Bueno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paillaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Unión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panguipulli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Lagos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futrono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Máfil</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:02</t>
+    <t xml:space="preserve">2026-09-27 21:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -495,13 +495,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>162486</v>
+        <v>7832</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>173420</v>
+        <v>7370</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>93.7</v>
+        <v>106.27</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5239</v>
+        <v>18159</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5439</v>
+        <v>17393</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>96.32</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +523,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>22013</v>
+        <v>15788</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>22775</v>
+        <v>15246</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>96.65</v>
+        <v>103.56</v>
       </c>
     </row>
     <row r="5">
@@ -537,13 +537,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10015</v>
+        <v>21061</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10270</v>
+        <v>20457</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>97.52</v>
+        <v>102.95</v>
       </c>
     </row>
     <row r="6">
@@ -551,13 +551,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>32819</v>
+        <v>36556</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>32814</v>
+        <v>35744</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>100.02</v>
+        <v>102.27</v>
       </c>
     </row>
     <row r="7">
@@ -565,13 +565,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>20916</v>
+        <v>40120</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>20649</v>
+        <v>39358</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>101.29</v>
+        <v>101.94</v>
       </c>
     </row>
     <row r="8">
@@ -579,13 +579,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>40120</v>
+        <v>20916</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>39358</v>
+        <v>20649</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>101.94</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="9">
@@ -593,13 +593,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>36556</v>
+        <v>32819</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>35744</v>
+        <v>32814</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>102.27</v>
+        <v>100.02</v>
       </c>
     </row>
     <row r="10">
@@ -607,13 +607,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>21061</v>
+        <v>10015</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>20457</v>
+        <v>10270</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>102.95</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="11">
@@ -621,13 +621,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>15788</v>
+        <v>22013</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>15246</v>
+        <v>22775</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>103.56</v>
+        <v>96.65</v>
       </c>
     </row>
     <row r="12">
@@ -635,13 +635,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>18159</v>
+        <v>5239</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>17393</v>
+        <v>5439</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>104.4</v>
+        <v>96.32</v>
       </c>
     </row>
     <row r="13">
@@ -649,13 +649,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>7832</v>
+        <v>162486</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7370</v>
+        <v>173420</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>106.27</v>
+        <v>93.7</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_los_rios.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_los_rios.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:44</t>
+    <t xml:space="preserve">2026-10-05 05:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
